--- a/Factures ventes enregistrées VC CONVENTION EDC.xlsx
+++ b/Factures ventes enregistrées VC CONVENTION EDC.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mgonline-my.sharepoint.com/personal/hamadi_chkondali_smg_com_tn/Documents/Documents/hamadi/grands compte/hamadi/dashbord convention/table vente/2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F992A1A-8952-41E0-B580-4210A59DB07B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{31537BCF-F14B-4E88-B89B-D8D26520EE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
